--- a/artfynd/A 57726-2024 artfynd.xlsx
+++ b/artfynd/A 57726-2024 artfynd.xlsx
@@ -905,11 +905,11 @@
         <v>115908090</v>
       </c>
       <c r="B4" t="n">
-        <v>57505</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rapport ska skrivas (för Rrk)</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 57726-2024 artfynd.xlsx
+++ b/artfynd/A 57726-2024 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>115908090</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 57726-2024 artfynd.xlsx
+++ b/artfynd/A 57726-2024 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>115908090</v>
       </c>
       <c r="B4" t="n">
-        <v>58024</v>
+        <v>58109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57726-2024 artfynd.xlsx
+++ b/artfynd/A 57726-2024 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>115908090</v>
       </c>
       <c r="B4" t="n">
-        <v>58109</v>
+        <v>58135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57726-2024 artfynd.xlsx
+++ b/artfynd/A 57726-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>92616397</v>
       </c>
       <c r="B2" t="n">
-        <v>56286</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,7 +695,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397969.2191700589</v>
+        <v>397969</v>
       </c>
       <c r="R2" t="n">
-        <v>6171677.566555605</v>
+        <v>6171678</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -799,54 +794,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111669058</v>
+        <v>65705637</v>
       </c>
       <c r="B3" t="n">
-        <v>87453</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1668</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Silkesslidskivling</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Volvariella bombycina</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Singer</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dalby Söderskogs nationalpark (Dalby Söderskogs nationalpark), Sk</t>
+          <t>Skrylleskogen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397941</v>
+        <v>398339</v>
       </c>
       <c r="R3" t="n">
-        <v>6171737</v>
+        <v>6171697</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +870,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2017-05-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2017-05-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,22 +900,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maria Rosberg </t>
+          <t>Oscar Stahle</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maria Rosberg </t>
+          <t>Oscar Stahle</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115908090</v>
+        <v>121793813</v>
       </c>
       <c r="B4" t="n">
-        <v>58135</v>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,23 +946,27 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>MTB-korsningen, Skryllegården, Sk</t>
+          <t>milspåret ca 5km, Skryllegården, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397825</v>
+        <v>398069</v>
       </c>
       <c r="R4" t="n">
-        <v>6171892</v>
+        <v>6171879</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,22 +993,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ivrigt lockande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,15 +1028,381 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Håkan Bergström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Bergström, Sara Agrup</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>71354563</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skrylleskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>398337</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6171821</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-05-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-05-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Satt och sjöng på en torr grangren invid 10 km spåret</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Oscar Stahle</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Oscar Stahle</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>78075138</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skrylleskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>398080</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6171863</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-05-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-05-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Såg tre sjungande grönsångare längs milspåret på Skrylle. Vid ett par olika platser men framför allt vid ca 5 km på milspåret.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Oscar Stahle</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Oscar Stahle</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>115908090</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>MTB-korsningen, Skryllegården, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>397825</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6171892</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>John Mo</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>John Mo</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
